--- a/Pytestworkspace/DataDriven_Excel/ExcelFiles/Logindata.xlsx
+++ b/Pytestworkspace/DataDriven_Excel/ExcelFiles/Logindata.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\PythonSelenium\Pytestworkspace\DataDriven_Excel\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE040001-9DB1-477E-8CF3-E2F21136AB6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6239C522-0A13-4E96-B2E9-E0DDD014DF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
+    <sheet name="Tutorialsninja" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>username</t>
   </si>
@@ -37,6 +38,12 @@
   </si>
   <si>
     <t>Admi12</t>
+  </si>
+  <si>
+    <t>jothika@gmail.com</t>
+  </si>
+  <si>
+    <t>admin5</t>
   </si>
 </sst>
 </file>
@@ -398,4 +405,33 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F09956-AF7F-4C07-A384-253A412F04E1}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{9DAD78B4-4499-410B-A95B-66BE07D9A1AB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>